--- a/outputs/daily/hr_rankings_2026-10-16.xlsx
+++ b/outputs/daily/hr_rankings_2026-10-16.xlsx
@@ -768,11 +768,23 @@
           <t>3</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Shawn Armstrong</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>542888</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L2" t="n">
-        <v>54.7</v>
+        <v>51.5</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -790,10 +802,10 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>62</v>
+        <v>61.9</v>
       </c>
       <c r="Q2" t="n">
-        <v>41.2</v>
+        <v>32</v>
       </c>
       <c r="R2" t="n">
         <v>27.6</v>
@@ -802,7 +814,7 @@
         <v>92.09999999999999</v>
       </c>
       <c r="T2" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U2" t="n">
         <v>37.8</v>
@@ -844,7 +856,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr"/>
@@ -881,7 +893,7 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
@@ -926,7 +938,7 @@
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>79.13</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
@@ -954,12 +966,36 @@
           <t>0.2549</t>
         </is>
       </c>
-      <c r="BA2" t="inlineStr"/>
-      <c r="BB2" t="inlineStr"/>
-      <c r="BC2" t="inlineStr"/>
-      <c r="BD2" t="inlineStr"/>
-      <c r="BE2" t="inlineStr"/>
-      <c r="BF2" t="inlineStr"/>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>35.04</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>88.35</t>
+        </is>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>0.3695</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>0.1577</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>29.92</t>
+        </is>
+      </c>
       <c r="BG2" t="inlineStr"/>
       <c r="BH2" t="inlineStr"/>
       <c r="BI2" t="inlineStr">
@@ -1008,11 +1044,23 @@
           <t>2</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Shawn Armstrong</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>542888</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L3" t="n">
-        <v>50.4</v>
+        <v>50</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1026,14 +1074,14 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P3" t="n">
         <v>48.9</v>
       </c>
       <c r="Q3" t="n">
-        <v>41.2</v>
+        <v>32</v>
       </c>
       <c r="R3" t="n">
         <v>27.6</v>
@@ -1042,7 +1090,7 @@
         <v>95.5</v>
       </c>
       <c r="T3" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U3" t="n">
         <v>28.9</v>
@@ -1084,7 +1132,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr"/>
@@ -1121,7 +1169,7 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
@@ -1194,12 +1242,36 @@
           <t>0.1639</t>
         </is>
       </c>
-      <c r="BA3" t="inlineStr"/>
-      <c r="BB3" t="inlineStr"/>
-      <c r="BC3" t="inlineStr"/>
-      <c r="BD3" t="inlineStr"/>
-      <c r="BE3" t="inlineStr"/>
-      <c r="BF3" t="inlineStr"/>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>35.04</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>88.35</t>
+        </is>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>0.3695</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>0.1577</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>29.92</t>
+        </is>
+      </c>
       <c r="BG3" t="inlineStr"/>
       <c r="BH3" t="inlineStr"/>
       <c r="BI3" t="inlineStr">
@@ -1423,7 +1495,7 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>72.81</t>
+          <t>72.74</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
@@ -1800,11 +1872,23 @@
           <t>6</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Shawn Armstrong</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>542888</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L6" t="n">
-        <v>46.6</v>
+        <v>46.2</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1818,14 +1902,14 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P6" t="n">
         <v>43.6</v>
       </c>
       <c r="Q6" t="n">
-        <v>41.2</v>
+        <v>32</v>
       </c>
       <c r="R6" t="n">
         <v>27.6</v>
@@ -1834,7 +1918,7 @@
         <v>71.7</v>
       </c>
       <c r="T6" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U6" t="n">
         <v>54.9</v>
@@ -1876,7 +1960,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr"/>
@@ -1913,7 +1997,7 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
@@ -1986,12 +2070,36 @@
           <t>0.2134</t>
         </is>
       </c>
-      <c r="BA6" t="inlineStr"/>
-      <c r="BB6" t="inlineStr"/>
-      <c r="BC6" t="inlineStr"/>
-      <c r="BD6" t="inlineStr"/>
-      <c r="BE6" t="inlineStr"/>
-      <c r="BF6" t="inlineStr"/>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>35.04</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>88.35</t>
+        </is>
+      </c>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>0.3695</t>
+        </is>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>0.1577</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>29.92</t>
+        </is>
+      </c>
       <c r="BG6" t="inlineStr"/>
       <c r="BH6" t="inlineStr"/>
       <c r="BI6" t="inlineStr">
@@ -2007,24 +2115,24 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>650490</t>
+          <t>663993</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Yandy Diaz</t>
+          <t>Nathaniel Lowe</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>2026-10-17T00:00:00Z</t>
@@ -2037,14 +2145,26 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Nick Martinez</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>607259</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L7" t="n">
-        <v>46.4</v>
+        <v>43.5</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -2058,26 +2178,26 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>41</v>
+        <v>36.3</v>
       </c>
       <c r="Q7" t="n">
-        <v>41.2</v>
+        <v>34.3</v>
       </c>
       <c r="R7" t="n">
         <v>27.6</v>
       </c>
       <c r="S7" t="n">
-        <v>88.7</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T7" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U7" t="n">
-        <v>20.9</v>
+        <v>10.1</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
@@ -2091,7 +2211,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -2116,7 +2236,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr"/>
@@ -2133,12 +2253,12 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
@@ -2148,12 +2268,12 @@
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/27, 0 HR</t>
+          <t>Last 7 games: 3/16, 0 HR</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
@@ -2163,75 +2283,99 @@
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>7.46</t>
+          <t>7.98</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>49.42</t>
+          <t>41.43</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>91.53</t>
+          <t>89.42</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>103.1694</t>
+          <t>100.8354</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.4453</t>
+          <t>0.4178</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>0.1621</t>
+          <t>0.1618</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>0.3484</t>
+          <t>0.3254</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>73.86</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>37.37</t>
+          <t>37.96</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>23.46</t>
+          <t>34.82</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>19.65</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>0.1617</t>
-        </is>
-      </c>
-      <c r="BA7" t="inlineStr"/>
-      <c r="BB7" t="inlineStr"/>
-      <c r="BC7" t="inlineStr"/>
-      <c r="BD7" t="inlineStr"/>
-      <c r="BE7" t="inlineStr"/>
-      <c r="BF7" t="inlineStr"/>
+          <t>0.1803</t>
+        </is>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>6.86</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>33.38</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>87.39</t>
+        </is>
+      </c>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>0.4114</t>
+        </is>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>0.1502</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>28.96</t>
+        </is>
+      </c>
       <c r="BG7" t="inlineStr"/>
       <c r="BH7" t="inlineStr"/>
       <c r="BI7" t="inlineStr">
@@ -2247,24 +2391,24 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>663993</t>
+          <t>650490</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Nathaniel Lowe</t>
+          <t>Yandy Diaz</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>2026-10-17T00:00:00Z</t>
@@ -2277,17 +2421,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Nick Martinez</t>
+          <t>Shawn Armstrong</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>607259</t>
+          <t>542888</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -2296,7 +2440,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>43.5</v>
+        <v>43.3</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2310,26 +2454,26 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>36.3</v>
+        <v>41</v>
       </c>
       <c r="Q8" t="n">
-        <v>34.3</v>
+        <v>32</v>
       </c>
       <c r="R8" t="n">
         <v>27.6</v>
       </c>
       <c r="S8" t="n">
-        <v>81.90000000000001</v>
+        <v>88.7</v>
       </c>
       <c r="T8" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U8" t="n">
-        <v>10.1</v>
+        <v>20.9</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
@@ -2343,7 +2487,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -2385,12 +2529,12 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -2400,12 +2544,12 @@
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/16, 0 HR</t>
+          <t>Last 7 games: 7/27, 0 HR</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
@@ -2415,97 +2559,97 @@
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>7.98</t>
+          <t>7.46</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>41.43</t>
+          <t>49.42</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>89.42</t>
+          <t>91.53</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>100.8354</t>
+          <t>103.1694</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.4178</t>
+          <t>0.4453</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>0.1618</t>
+          <t>0.1621</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.3254</t>
+          <t>0.3484</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>73.86</t>
+          <t>73.57</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>37.89</t>
+          <t>37.44</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>34.82</t>
+          <t>23.46</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>19.65</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>0.1803</t>
+          <t>0.1617</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>6.86</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>33.38</t>
+          <t>35.04</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>87.39</t>
+          <t>88.35</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>0.4114</t>
+          <t>0.3695</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>0.1502</t>
+          <t>0.1577</t>
         </is>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>28.96</t>
+          <t>29.92</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr"/>
@@ -3007,7 +3151,7 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>25.71</t>
+          <t>25.78</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
@@ -3351,24 +3495,24 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>689414</t>
+          <t>683953</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Liam Hicks</t>
+          <t>Travis Bazzana</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>2026-10-17T00:00:00Z</t>
@@ -3381,14 +3525,26 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Nick Martinez</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>607259</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L12" t="n">
-        <v>35.6</v>
+        <v>35.5</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -3402,26 +3558,26 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>7.8</v>
+        <v>20.9</v>
       </c>
       <c r="Q12" t="n">
-        <v>41.2</v>
+        <v>34.3</v>
       </c>
       <c r="R12" t="n">
         <v>27.6</v>
       </c>
       <c r="S12" t="n">
-        <v>90.40000000000001</v>
+        <v>59.8</v>
       </c>
       <c r="T12" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U12" t="n">
-        <v>19.5</v>
+        <v>12</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
@@ -3435,7 +3591,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -3460,7 +3616,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr"/>
@@ -3477,12 +3633,12 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -3492,12 +3648,12 @@
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 0 HR</t>
+          <t>Last 7 games: 5/25, 0 HR</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
@@ -3507,75 +3663,99 @@
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>27.28</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>96.0847</t>
+          <t>98.2866</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.3556</t>
+          <t>0.347</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>0.0997</t>
+          <t>0.123</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.3178</t>
+          <t>0.299</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>68.03</t>
+          <t>69.7</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>12.2</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>41.33</t>
+          <t>38.9</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>24.29</t>
+          <t>28.8</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>14.4</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>0.1347</t>
-        </is>
-      </c>
-      <c r="BA12" t="inlineStr"/>
-      <c r="BB12" t="inlineStr"/>
-      <c r="BC12" t="inlineStr"/>
-      <c r="BD12" t="inlineStr"/>
-      <c r="BE12" t="inlineStr"/>
-      <c r="BF12" t="inlineStr"/>
+          <t>0.163</t>
+        </is>
+      </c>
+      <c r="BA12" t="inlineStr">
+        <is>
+          <t>6.86</t>
+        </is>
+      </c>
+      <c r="BB12" t="inlineStr">
+        <is>
+          <t>33.38</t>
+        </is>
+      </c>
+      <c r="BC12" t="inlineStr">
+        <is>
+          <t>87.39</t>
+        </is>
+      </c>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>0.4114</t>
+        </is>
+      </c>
+      <c r="BE12" t="inlineStr">
+        <is>
+          <t>0.1502</t>
+        </is>
+      </c>
+      <c r="BF12" t="inlineStr">
+        <is>
+          <t>28.96</t>
+        </is>
+      </c>
       <c r="BG12" t="inlineStr"/>
       <c r="BH12" t="inlineStr"/>
       <c r="BI12" t="inlineStr">
@@ -3591,24 +3771,24 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>683953</t>
+          <t>689414</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Travis Bazzana</t>
+          <t>Liam Hicks</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>2026-10-17T00:00:00Z</t>
@@ -3621,17 +3801,17 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Nick Martinez</t>
+          <t>Shawn Armstrong</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>607259</t>
+          <t>542888</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -3640,7 +3820,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>35.5</v>
+        <v>35.2</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -3654,26 +3834,26 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>20.9</v>
+        <v>7.8</v>
       </c>
       <c r="Q13" t="n">
-        <v>34.3</v>
+        <v>32</v>
       </c>
       <c r="R13" t="n">
         <v>27.6</v>
       </c>
       <c r="S13" t="n">
-        <v>59.8</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T13" t="n">
         <v>80</v>
       </c>
       <c r="U13" t="n">
-        <v>12</v>
+        <v>19.5</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
@@ -3687,7 +3867,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -3712,7 +3892,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr"/>
@@ -3729,12 +3909,12 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
@@ -3744,12 +3924,12 @@
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/25, 0 HR</t>
+          <t>Last 7 games: 6/24, 0 HR</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
@@ -3759,97 +3939,97 @@
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>36.2</t>
+          <t>27.28</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>98.2866</t>
+          <t>96.0847</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>0.347</t>
+          <t>0.3556</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>0.0997</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.299</t>
+          <t>0.3178</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>68.03</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>41.33</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>28.8</t>
+          <t>24.29</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>14.4</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>0.163</t>
+          <t>0.1347</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>6.86</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>33.38</t>
+          <t>35.04</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>87.39</t>
+          <t>88.35</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>0.4114</t>
+          <t>0.3695</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
-          <t>0.1502</t>
+          <t>0.1577</t>
         </is>
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>28.96</t>
+          <t>29.92</t>
         </is>
       </c>
       <c r="BG13" t="inlineStr"/>
@@ -4143,24 +4323,24 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>676356</t>
+          <t>677587</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Jonny DeLuca</t>
+          <t>Brayan Rocchio</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>2026-10-17T00:00:00Z</t>
@@ -4173,14 +4353,26 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Nick Martinez</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>607259</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L15" t="n">
-        <v>34.8</v>
+        <v>32.5</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -4194,26 +4386,26 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup, Hot Hitter/Streak</t>
+          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>10.6</v>
+        <v>13.7</v>
       </c>
       <c r="Q15" t="n">
-        <v>41.2</v>
+        <v>32.5</v>
       </c>
       <c r="R15" t="n">
         <v>27.6</v>
       </c>
       <c r="S15" t="n">
-        <v>59.8</v>
+        <v>40.2</v>
       </c>
       <c r="T15" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="U15" t="n">
-        <v>70.59999999999999</v>
+        <v>72.7</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
@@ -4227,7 +4419,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -4252,7 +4444,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr"/>
@@ -4274,7 +4466,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
@@ -4289,7 +4481,7 @@
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
@@ -4299,75 +4491,99 @@
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>30.68</t>
+          <t>31.65</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>85.74</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>97.7063</t>
+          <t>97.253</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.3262</t>
+          <t>0.3524</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>0.0879</t>
+          <t>0.1067</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.2628</t>
+          <t>0.2943</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>72.68</t>
+          <t>69.79</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>27.96</t>
+          <t>6.45</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>43.71</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>22.55</t>
+          <t>25.23</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>0.151</t>
-        </is>
-      </c>
-      <c r="BA15" t="inlineStr"/>
-      <c r="BB15" t="inlineStr"/>
-      <c r="BC15" t="inlineStr"/>
-      <c r="BD15" t="inlineStr"/>
-      <c r="BE15" t="inlineStr"/>
-      <c r="BF15" t="inlineStr"/>
+          <t>0.1287</t>
+        </is>
+      </c>
+      <c r="BA15" t="inlineStr">
+        <is>
+          <t>6.86</t>
+        </is>
+      </c>
+      <c r="BB15" t="inlineStr">
+        <is>
+          <t>33.38</t>
+        </is>
+      </c>
+      <c r="BC15" t="inlineStr">
+        <is>
+          <t>87.39</t>
+        </is>
+      </c>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>0.4114</t>
+        </is>
+      </c>
+      <c r="BE15" t="inlineStr">
+        <is>
+          <t>0.1502</t>
+        </is>
+      </c>
+      <c r="BF15" t="inlineStr">
+        <is>
+          <t>28.96</t>
+        </is>
+      </c>
       <c r="BG15" t="inlineStr"/>
       <c r="BH15" t="inlineStr"/>
       <c r="BI15" t="inlineStr">
@@ -4383,24 +4599,24 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>677587</t>
+          <t>680700</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Brayan Rocchio</t>
+          <t>Richie Palacios</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>2026-10-17T00:00:00Z</t>
@@ -4413,17 +4629,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Nick Martinez</t>
+          <t>Shawn Armstrong</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>607259</t>
+          <t>542888</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -4432,7 +4648,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>32.5</v>
+        <v>31.8</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -4446,26 +4662,26 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>13.7</v>
+        <v>15.4</v>
       </c>
       <c r="Q16" t="n">
-        <v>32.5</v>
+        <v>32</v>
       </c>
       <c r="R16" t="n">
         <v>27.6</v>
       </c>
       <c r="S16" t="n">
-        <v>40.2</v>
+        <v>47.9</v>
       </c>
       <c r="T16" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U16" t="n">
-        <v>72.7</v>
+        <v>19.5</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
@@ -4479,7 +4695,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -4521,27 +4737,27 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 5/20, 0 HR</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
@@ -4551,97 +4767,97 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>31.65</t>
+          <t>33.39</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>87.31</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>97.253</t>
+          <t>97.1084</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.3524</t>
+          <t>0.3655</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>0.1067</t>
+          <t>0.1018</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.2943</t>
+          <t>0.3213</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>69.79</t>
+          <t>68.91</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>6.45</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>43.71</t>
+          <t>37.09</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>25.23</t>
+          <t>20.98</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>0.1287</t>
+          <t>0.133</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>6.86</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>33.38</t>
+          <t>35.04</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>87.39</t>
+          <t>88.35</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>0.4114</t>
+          <t>0.3695</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
-          <t>0.1502</t>
+          <t>0.1577</t>
         </is>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>28.96</t>
+          <t>29.92</t>
         </is>
       </c>
       <c r="BG16" t="inlineStr"/>
@@ -4659,12 +4875,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>680700</t>
+          <t>676356</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Richie Palacios</t>
+          <t>Jonny DeLuca</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -4689,14 +4905,26 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Shawn Armstrong</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>542888</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L17" t="n">
-        <v>32.2</v>
+        <v>31.7</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -4710,26 +4938,26 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>15.4</v>
+        <v>10.6</v>
       </c>
       <c r="Q17" t="n">
-        <v>41.2</v>
+        <v>32</v>
       </c>
       <c r="R17" t="n">
         <v>27.6</v>
       </c>
       <c r="S17" t="n">
-        <v>47.9</v>
+        <v>59.8</v>
       </c>
       <c r="T17" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U17" t="n">
-        <v>19.5</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
@@ -4743,7 +4971,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -4768,7 +4996,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr"/>
@@ -4785,27 +5013,27 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/20, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
@@ -4815,75 +5043,99 @@
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>4.57</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>33.39</t>
+          <t>30.68</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>87.31</t>
+          <t>85.74</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>97.1084</t>
+          <t>97.7063</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.3655</t>
+          <t>0.3262</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>0.1018</t>
+          <t>0.0879</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.3213</t>
+          <t>0.2628</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>68.91</t>
+          <t>72.75</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>28.03</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>37.09</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>20.98</t>
+          <t>22.55</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>0.133</t>
-        </is>
-      </c>
-      <c r="BA17" t="inlineStr"/>
-      <c r="BB17" t="inlineStr"/>
-      <c r="BC17" t="inlineStr"/>
-      <c r="BD17" t="inlineStr"/>
-      <c r="BE17" t="inlineStr"/>
-      <c r="BF17" t="inlineStr"/>
+          <t>0.151</t>
+        </is>
+      </c>
+      <c r="BA17" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="BB17" t="inlineStr">
+        <is>
+          <t>35.04</t>
+        </is>
+      </c>
+      <c r="BC17" t="inlineStr">
+        <is>
+          <t>88.35</t>
+        </is>
+      </c>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>0.3695</t>
+        </is>
+      </c>
+      <c r="BE17" t="inlineStr">
+        <is>
+          <t>0.1577</t>
+        </is>
+      </c>
+      <c r="BF17" t="inlineStr">
+        <is>
+          <t>29.92</t>
+        </is>
+      </c>
       <c r="BG17" t="inlineStr"/>
       <c r="BH17" t="inlineStr"/>
       <c r="BI17" t="inlineStr">
@@ -4932,11 +5184,23 @@
           <t>5</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Shawn Armstrong</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>542888</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L18" t="n">
-        <v>31.8</v>
+        <v>31.3</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -4950,14 +5214,14 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P18" t="n">
         <v>0.2</v>
       </c>
       <c r="Q18" t="n">
-        <v>41.2</v>
+        <v>32</v>
       </c>
       <c r="R18" t="n">
         <v>27.6</v>
@@ -4966,7 +5230,7 @@
         <v>81.90000000000001</v>
       </c>
       <c r="T18" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U18" t="n">
         <v>15.3</v>
@@ -5008,7 +5272,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr"/>
@@ -5045,7 +5309,7 @@
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
@@ -5118,12 +5382,36 @@
           <t>0.05</t>
         </is>
       </c>
-      <c r="BA18" t="inlineStr"/>
-      <c r="BB18" t="inlineStr"/>
-      <c r="BC18" t="inlineStr"/>
-      <c r="BD18" t="inlineStr"/>
-      <c r="BE18" t="inlineStr"/>
-      <c r="BF18" t="inlineStr"/>
+      <c r="BA18" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="BB18" t="inlineStr">
+        <is>
+          <t>35.04</t>
+        </is>
+      </c>
+      <c r="BC18" t="inlineStr">
+        <is>
+          <t>88.35</t>
+        </is>
+      </c>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>0.3695</t>
+        </is>
+      </c>
+      <c r="BE18" t="inlineStr">
+        <is>
+          <t>0.1577</t>
+        </is>
+      </c>
+      <c r="BF18" t="inlineStr">
+        <is>
+          <t>29.92</t>
+        </is>
+      </c>
       <c r="BG18" t="inlineStr"/>
       <c r="BH18" t="inlineStr"/>
       <c r="BI18" t="inlineStr">
@@ -5172,11 +5460,23 @@
           <t>9</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Shawn Armstrong</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>542888</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L19" t="n">
-        <v>29.4</v>
+        <v>27.3</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -5197,7 +5497,7 @@
         <v>5.6</v>
       </c>
       <c r="Q19" t="n">
-        <v>40.2</v>
+        <v>31.5</v>
       </c>
       <c r="R19" t="n">
         <v>27.6</v>
@@ -5248,7 +5548,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr"/>
@@ -5285,7 +5585,7 @@
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
@@ -5358,12 +5658,36 @@
           <t>0.0829</t>
         </is>
       </c>
-      <c r="BA19" t="inlineStr"/>
-      <c r="BB19" t="inlineStr"/>
-      <c r="BC19" t="inlineStr"/>
-      <c r="BD19" t="inlineStr"/>
-      <c r="BE19" t="inlineStr"/>
-      <c r="BF19" t="inlineStr"/>
+      <c r="BA19" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="BB19" t="inlineStr">
+        <is>
+          <t>35.04</t>
+        </is>
+      </c>
+      <c r="BC19" t="inlineStr">
+        <is>
+          <t>88.35</t>
+        </is>
+      </c>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>0.3695</t>
+        </is>
+      </c>
+      <c r="BE19" t="inlineStr">
+        <is>
+          <t>0.1577</t>
+        </is>
+      </c>
+      <c r="BF19" t="inlineStr">
+        <is>
+          <t>29.92</t>
+        </is>
+      </c>
       <c r="BG19" t="inlineStr"/>
       <c r="BH19" t="inlineStr"/>
       <c r="BI19" t="inlineStr">
@@ -5738,11 +6062,23 @@
           <t>3</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Shawn Armstrong</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>542888</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L2" t="n">
-        <v>54.7</v>
+        <v>51.5</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -5760,10 +6096,10 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>62</v>
+        <v>61.9</v>
       </c>
       <c r="Q2" t="n">
-        <v>41.2</v>
+        <v>32</v>
       </c>
       <c r="R2" t="n">
         <v>27.6</v>
@@ -5772,7 +6108,7 @@
         <v>92.09999999999999</v>
       </c>
       <c r="T2" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U2" t="n">
         <v>37.8</v>
@@ -5814,7 +6150,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr"/>
@@ -5851,7 +6187,7 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
@@ -5896,7 +6232,7 @@
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>79.13</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
@@ -5924,12 +6260,36 @@
           <t>0.2549</t>
         </is>
       </c>
-      <c r="BA2" t="inlineStr"/>
-      <c r="BB2" t="inlineStr"/>
-      <c r="BC2" t="inlineStr"/>
-      <c r="BD2" t="inlineStr"/>
-      <c r="BE2" t="inlineStr"/>
-      <c r="BF2" t="inlineStr"/>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>35.04</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>88.35</t>
+        </is>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>0.3695</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>0.1577</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>29.92</t>
+        </is>
+      </c>
       <c r="BG2" t="inlineStr"/>
       <c r="BH2" t="inlineStr"/>
       <c r="BI2" t="inlineStr">
@@ -5978,11 +6338,23 @@
           <t>2</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Shawn Armstrong</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>542888</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L3" t="n">
-        <v>50.4</v>
+        <v>50</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -5996,14 +6368,14 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P3" t="n">
         <v>48.9</v>
       </c>
       <c r="Q3" t="n">
-        <v>41.2</v>
+        <v>32</v>
       </c>
       <c r="R3" t="n">
         <v>27.6</v>
@@ -6012,7 +6384,7 @@
         <v>95.5</v>
       </c>
       <c r="T3" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U3" t="n">
         <v>28.9</v>
@@ -6054,7 +6426,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr"/>
@@ -6091,7 +6463,7 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
@@ -6164,12 +6536,36 @@
           <t>0.1639</t>
         </is>
       </c>
-      <c r="BA3" t="inlineStr"/>
-      <c r="BB3" t="inlineStr"/>
-      <c r="BC3" t="inlineStr"/>
-      <c r="BD3" t="inlineStr"/>
-      <c r="BE3" t="inlineStr"/>
-      <c r="BF3" t="inlineStr"/>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>35.04</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>88.35</t>
+        </is>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>0.3695</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>0.1577</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>29.92</t>
+        </is>
+      </c>
       <c r="BG3" t="inlineStr"/>
       <c r="BH3" t="inlineStr"/>
       <c r="BI3" t="inlineStr">
@@ -6393,7 +6789,7 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>72.81</t>
+          <t>72.74</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
@@ -6770,11 +7166,23 @@
           <t>6</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Shawn Armstrong</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>542888</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L6" t="n">
-        <v>46.6</v>
+        <v>46.2</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -6788,14 +7196,14 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P6" t="n">
         <v>43.6</v>
       </c>
       <c r="Q6" t="n">
-        <v>41.2</v>
+        <v>32</v>
       </c>
       <c r="R6" t="n">
         <v>27.6</v>
@@ -6804,7 +7212,7 @@
         <v>71.7</v>
       </c>
       <c r="T6" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U6" t="n">
         <v>54.9</v>
@@ -6846,7 +7254,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr"/>
@@ -6883,7 +7291,7 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
@@ -6956,12 +7364,36 @@
           <t>0.2134</t>
         </is>
       </c>
-      <c r="BA6" t="inlineStr"/>
-      <c r="BB6" t="inlineStr"/>
-      <c r="BC6" t="inlineStr"/>
-      <c r="BD6" t="inlineStr"/>
-      <c r="BE6" t="inlineStr"/>
-      <c r="BF6" t="inlineStr"/>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>35.04</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>88.35</t>
+        </is>
+      </c>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>0.3695</t>
+        </is>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>0.1577</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>29.92</t>
+        </is>
+      </c>
       <c r="BG6" t="inlineStr"/>
       <c r="BH6" t="inlineStr"/>
       <c r="BI6" t="inlineStr">
@@ -6977,24 +7409,24 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>650490</t>
+          <t>663993</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Yandy Diaz</t>
+          <t>Nathaniel Lowe</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>2026-10-17T00:00:00Z</t>
@@ -7007,14 +7439,26 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Nick Martinez</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>607259</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L7" t="n">
-        <v>46.4</v>
+        <v>43.5</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -7028,26 +7472,26 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>41</v>
+        <v>36.3</v>
       </c>
       <c r="Q7" t="n">
-        <v>41.2</v>
+        <v>34.3</v>
       </c>
       <c r="R7" t="n">
         <v>27.6</v>
       </c>
       <c r="S7" t="n">
-        <v>88.7</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T7" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U7" t="n">
-        <v>20.9</v>
+        <v>10.1</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
@@ -7061,7 +7505,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -7086,7 +7530,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr"/>
@@ -7103,12 +7547,12 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
@@ -7118,12 +7562,12 @@
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/27, 0 HR</t>
+          <t>Last 7 games: 3/16, 0 HR</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
@@ -7133,75 +7577,99 @@
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>7.46</t>
+          <t>7.98</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>49.42</t>
+          <t>41.43</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>91.53</t>
+          <t>89.42</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>103.1694</t>
+          <t>100.8354</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.4453</t>
+          <t>0.4178</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>0.1621</t>
+          <t>0.1618</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>0.3484</t>
+          <t>0.3254</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>73.86</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>37.37</t>
+          <t>37.96</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>23.46</t>
+          <t>34.82</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>19.65</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>0.1617</t>
-        </is>
-      </c>
-      <c r="BA7" t="inlineStr"/>
-      <c r="BB7" t="inlineStr"/>
-      <c r="BC7" t="inlineStr"/>
-      <c r="BD7" t="inlineStr"/>
-      <c r="BE7" t="inlineStr"/>
-      <c r="BF7" t="inlineStr"/>
+          <t>0.1803</t>
+        </is>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>6.86</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>33.38</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>87.39</t>
+        </is>
+      </c>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>0.4114</t>
+        </is>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>0.1502</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>28.96</t>
+        </is>
+      </c>
       <c r="BG7" t="inlineStr"/>
       <c r="BH7" t="inlineStr"/>
       <c r="BI7" t="inlineStr">
@@ -7217,24 +7685,24 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>663993</t>
+          <t>650490</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Nathaniel Lowe</t>
+          <t>Yandy Diaz</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>2026-10-17T00:00:00Z</t>
@@ -7247,17 +7715,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Nick Martinez</t>
+          <t>Shawn Armstrong</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>607259</t>
+          <t>542888</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -7266,7 +7734,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>43.5</v>
+        <v>43.3</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -7280,26 +7748,26 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>36.3</v>
+        <v>41</v>
       </c>
       <c r="Q8" t="n">
-        <v>34.3</v>
+        <v>32</v>
       </c>
       <c r="R8" t="n">
         <v>27.6</v>
       </c>
       <c r="S8" t="n">
-        <v>81.90000000000001</v>
+        <v>88.7</v>
       </c>
       <c r="T8" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U8" t="n">
-        <v>10.1</v>
+        <v>20.9</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
@@ -7313,7 +7781,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -7355,12 +7823,12 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -7370,12 +7838,12 @@
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/16, 0 HR</t>
+          <t>Last 7 games: 7/27, 0 HR</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
@@ -7385,97 +7853,97 @@
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>7.98</t>
+          <t>7.46</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>41.43</t>
+          <t>49.42</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>89.42</t>
+          <t>91.53</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>100.8354</t>
+          <t>103.1694</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.4178</t>
+          <t>0.4453</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>0.1618</t>
+          <t>0.1621</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.3254</t>
+          <t>0.3484</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>73.86</t>
+          <t>73.57</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>37.89</t>
+          <t>37.44</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>34.82</t>
+          <t>23.46</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>19.65</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>0.1803</t>
+          <t>0.1617</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>6.86</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>33.38</t>
+          <t>35.04</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>87.39</t>
+          <t>88.35</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>0.4114</t>
+          <t>0.3695</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>0.1502</t>
+          <t>0.1577</t>
         </is>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>28.96</t>
+          <t>29.92</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr"/>
@@ -7977,7 +8445,7 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>25.71</t>
+          <t>25.78</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
@@ -8321,24 +8789,24 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>689414</t>
+          <t>683953</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Liam Hicks</t>
+          <t>Travis Bazzana</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>2026-10-17T00:00:00Z</t>
@@ -8351,14 +8819,26 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Nick Martinez</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>607259</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L12" t="n">
-        <v>35.6</v>
+        <v>35.5</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -8372,26 +8852,26 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>7.8</v>
+        <v>20.9</v>
       </c>
       <c r="Q12" t="n">
-        <v>41.2</v>
+        <v>34.3</v>
       </c>
       <c r="R12" t="n">
         <v>27.6</v>
       </c>
       <c r="S12" t="n">
-        <v>90.40000000000001</v>
+        <v>59.8</v>
       </c>
       <c r="T12" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U12" t="n">
-        <v>19.5</v>
+        <v>12</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
@@ -8405,7 +8885,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -8430,7 +8910,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr"/>
@@ -8447,12 +8927,12 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -8462,12 +8942,12 @@
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 0 HR</t>
+          <t>Last 7 games: 5/25, 0 HR</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
@@ -8477,75 +8957,99 @@
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>27.28</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>96.0847</t>
+          <t>98.2866</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.3556</t>
+          <t>0.347</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>0.0997</t>
+          <t>0.123</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.3178</t>
+          <t>0.299</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>68.03</t>
+          <t>69.7</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>12.2</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>41.33</t>
+          <t>38.9</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>24.29</t>
+          <t>28.8</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>14.4</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>0.1347</t>
-        </is>
-      </c>
-      <c r="BA12" t="inlineStr"/>
-      <c r="BB12" t="inlineStr"/>
-      <c r="BC12" t="inlineStr"/>
-      <c r="BD12" t="inlineStr"/>
-      <c r="BE12" t="inlineStr"/>
-      <c r="BF12" t="inlineStr"/>
+          <t>0.163</t>
+        </is>
+      </c>
+      <c r="BA12" t="inlineStr">
+        <is>
+          <t>6.86</t>
+        </is>
+      </c>
+      <c r="BB12" t="inlineStr">
+        <is>
+          <t>33.38</t>
+        </is>
+      </c>
+      <c r="BC12" t="inlineStr">
+        <is>
+          <t>87.39</t>
+        </is>
+      </c>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>0.4114</t>
+        </is>
+      </c>
+      <c r="BE12" t="inlineStr">
+        <is>
+          <t>0.1502</t>
+        </is>
+      </c>
+      <c r="BF12" t="inlineStr">
+        <is>
+          <t>28.96</t>
+        </is>
+      </c>
       <c r="BG12" t="inlineStr"/>
       <c r="BH12" t="inlineStr"/>
       <c r="BI12" t="inlineStr">
@@ -8561,24 +9065,24 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>683953</t>
+          <t>689414</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Travis Bazzana</t>
+          <t>Liam Hicks</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>2026-10-17T00:00:00Z</t>
@@ -8591,17 +9095,17 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Nick Martinez</t>
+          <t>Shawn Armstrong</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>607259</t>
+          <t>542888</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -8610,7 +9114,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>35.5</v>
+        <v>35.2</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -8624,26 +9128,26 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>20.9</v>
+        <v>7.8</v>
       </c>
       <c r="Q13" t="n">
-        <v>34.3</v>
+        <v>32</v>
       </c>
       <c r="R13" t="n">
         <v>27.6</v>
       </c>
       <c r="S13" t="n">
-        <v>59.8</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T13" t="n">
         <v>80</v>
       </c>
       <c r="U13" t="n">
-        <v>12</v>
+        <v>19.5</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
@@ -8657,7 +9161,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -8682,7 +9186,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr"/>
@@ -8699,12 +9203,12 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
@@ -8714,12 +9218,12 @@
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/25, 0 HR</t>
+          <t>Last 7 games: 6/24, 0 HR</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
@@ -8729,97 +9233,97 @@
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>36.2</t>
+          <t>27.28</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>98.2866</t>
+          <t>96.0847</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>0.347</t>
+          <t>0.3556</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>0.0997</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.299</t>
+          <t>0.3178</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>68.03</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>41.33</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>28.8</t>
+          <t>24.29</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>14.4</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>0.163</t>
+          <t>0.1347</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>6.86</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>33.38</t>
+          <t>35.04</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>87.39</t>
+          <t>88.35</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>0.4114</t>
+          <t>0.3695</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
-          <t>0.1502</t>
+          <t>0.1577</t>
         </is>
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>28.96</t>
+          <t>29.92</t>
         </is>
       </c>
       <c r="BG13" t="inlineStr"/>
@@ -9113,24 +9617,24 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>676356</t>
+          <t>677587</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Jonny DeLuca</t>
+          <t>Brayan Rocchio</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>2026-10-17T00:00:00Z</t>
@@ -9143,14 +9647,26 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Nick Martinez</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>607259</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L15" t="n">
-        <v>34.8</v>
+        <v>32.5</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -9164,26 +9680,26 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup, Hot Hitter/Streak</t>
+          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>10.6</v>
+        <v>13.7</v>
       </c>
       <c r="Q15" t="n">
-        <v>41.2</v>
+        <v>32.5</v>
       </c>
       <c r="R15" t="n">
         <v>27.6</v>
       </c>
       <c r="S15" t="n">
-        <v>59.8</v>
+        <v>40.2</v>
       </c>
       <c r="T15" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="U15" t="n">
-        <v>70.59999999999999</v>
+        <v>72.7</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
@@ -9197,7 +9713,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -9222,7 +9738,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr"/>
@@ -9244,7 +9760,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
@@ -9259,7 +9775,7 @@
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
@@ -9269,75 +9785,99 @@
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>30.68</t>
+          <t>31.65</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>85.74</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>97.7063</t>
+          <t>97.253</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.3262</t>
+          <t>0.3524</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>0.0879</t>
+          <t>0.1067</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.2628</t>
+          <t>0.2943</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>72.68</t>
+          <t>69.79</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>27.96</t>
+          <t>6.45</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>43.71</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>22.55</t>
+          <t>25.23</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>0.151</t>
-        </is>
-      </c>
-      <c r="BA15" t="inlineStr"/>
-      <c r="BB15" t="inlineStr"/>
-      <c r="BC15" t="inlineStr"/>
-      <c r="BD15" t="inlineStr"/>
-      <c r="BE15" t="inlineStr"/>
-      <c r="BF15" t="inlineStr"/>
+          <t>0.1287</t>
+        </is>
+      </c>
+      <c r="BA15" t="inlineStr">
+        <is>
+          <t>6.86</t>
+        </is>
+      </c>
+      <c r="BB15" t="inlineStr">
+        <is>
+          <t>33.38</t>
+        </is>
+      </c>
+      <c r="BC15" t="inlineStr">
+        <is>
+          <t>87.39</t>
+        </is>
+      </c>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>0.4114</t>
+        </is>
+      </c>
+      <c r="BE15" t="inlineStr">
+        <is>
+          <t>0.1502</t>
+        </is>
+      </c>
+      <c r="BF15" t="inlineStr">
+        <is>
+          <t>28.96</t>
+        </is>
+      </c>
       <c r="BG15" t="inlineStr"/>
       <c r="BH15" t="inlineStr"/>
       <c r="BI15" t="inlineStr">
@@ -9353,24 +9893,24 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>677587</t>
+          <t>680700</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Brayan Rocchio</t>
+          <t>Richie Palacios</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>2026-10-17T00:00:00Z</t>
@@ -9383,17 +9923,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Nick Martinez</t>
+          <t>Shawn Armstrong</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>607259</t>
+          <t>542888</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -9402,7 +9942,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>32.5</v>
+        <v>31.8</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -9416,26 +9956,26 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>13.7</v>
+        <v>15.4</v>
       </c>
       <c r="Q16" t="n">
-        <v>32.5</v>
+        <v>32</v>
       </c>
       <c r="R16" t="n">
         <v>27.6</v>
       </c>
       <c r="S16" t="n">
-        <v>40.2</v>
+        <v>47.9</v>
       </c>
       <c r="T16" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U16" t="n">
-        <v>72.7</v>
+        <v>19.5</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
@@ -9449,7 +9989,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -9491,27 +10031,27 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 5/20, 0 HR</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
@@ -9521,97 +10061,97 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>31.65</t>
+          <t>33.39</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>87.31</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>97.253</t>
+          <t>97.1084</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.3524</t>
+          <t>0.3655</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>0.1067</t>
+          <t>0.1018</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.2943</t>
+          <t>0.3213</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>69.79</t>
+          <t>68.91</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>6.45</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>43.71</t>
+          <t>37.09</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>25.23</t>
+          <t>20.98</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>0.1287</t>
+          <t>0.133</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>6.86</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>33.38</t>
+          <t>35.04</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>87.39</t>
+          <t>88.35</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>0.4114</t>
+          <t>0.3695</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
-          <t>0.1502</t>
+          <t>0.1577</t>
         </is>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>28.96</t>
+          <t>29.92</t>
         </is>
       </c>
       <c r="BG16" t="inlineStr"/>
@@ -9629,12 +10169,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>680700</t>
+          <t>676356</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Richie Palacios</t>
+          <t>Jonny DeLuca</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -9659,14 +10199,26 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Shawn Armstrong</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>542888</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L17" t="n">
-        <v>32.2</v>
+        <v>31.7</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -9680,26 +10232,26 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>15.4</v>
+        <v>10.6</v>
       </c>
       <c r="Q17" t="n">
-        <v>41.2</v>
+        <v>32</v>
       </c>
       <c r="R17" t="n">
         <v>27.6</v>
       </c>
       <c r="S17" t="n">
-        <v>47.9</v>
+        <v>59.8</v>
       </c>
       <c r="T17" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U17" t="n">
-        <v>19.5</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
@@ -9713,7 +10265,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -9738,7 +10290,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr"/>
@@ -9755,27 +10307,27 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/20, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
@@ -9785,75 +10337,99 @@
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>4.57</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>33.39</t>
+          <t>30.68</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>87.31</t>
+          <t>85.74</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>97.1084</t>
+          <t>97.7063</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.3655</t>
+          <t>0.3262</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>0.1018</t>
+          <t>0.0879</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.3213</t>
+          <t>0.2628</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>68.91</t>
+          <t>72.75</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>28.03</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>37.09</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>20.98</t>
+          <t>22.55</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>0.133</t>
-        </is>
-      </c>
-      <c r="BA17" t="inlineStr"/>
-      <c r="BB17" t="inlineStr"/>
-      <c r="BC17" t="inlineStr"/>
-      <c r="BD17" t="inlineStr"/>
-      <c r="BE17" t="inlineStr"/>
-      <c r="BF17" t="inlineStr"/>
+          <t>0.151</t>
+        </is>
+      </c>
+      <c r="BA17" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="BB17" t="inlineStr">
+        <is>
+          <t>35.04</t>
+        </is>
+      </c>
+      <c r="BC17" t="inlineStr">
+        <is>
+          <t>88.35</t>
+        </is>
+      </c>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>0.3695</t>
+        </is>
+      </c>
+      <c r="BE17" t="inlineStr">
+        <is>
+          <t>0.1577</t>
+        </is>
+      </c>
+      <c r="BF17" t="inlineStr">
+        <is>
+          <t>29.92</t>
+        </is>
+      </c>
       <c r="BG17" t="inlineStr"/>
       <c r="BH17" t="inlineStr"/>
       <c r="BI17" t="inlineStr">
@@ -9902,11 +10478,23 @@
           <t>5</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Shawn Armstrong</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>542888</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L18" t="n">
-        <v>31.8</v>
+        <v>31.3</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -9920,14 +10508,14 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P18" t="n">
         <v>0.2</v>
       </c>
       <c r="Q18" t="n">
-        <v>41.2</v>
+        <v>32</v>
       </c>
       <c r="R18" t="n">
         <v>27.6</v>
@@ -9936,7 +10524,7 @@
         <v>81.90000000000001</v>
       </c>
       <c r="T18" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U18" t="n">
         <v>15.3</v>
@@ -9978,7 +10566,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr"/>
@@ -10015,7 +10603,7 @@
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
@@ -10088,12 +10676,36 @@
           <t>0.05</t>
         </is>
       </c>
-      <c r="BA18" t="inlineStr"/>
-      <c r="BB18" t="inlineStr"/>
-      <c r="BC18" t="inlineStr"/>
-      <c r="BD18" t="inlineStr"/>
-      <c r="BE18" t="inlineStr"/>
-      <c r="BF18" t="inlineStr"/>
+      <c r="BA18" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="BB18" t="inlineStr">
+        <is>
+          <t>35.04</t>
+        </is>
+      </c>
+      <c r="BC18" t="inlineStr">
+        <is>
+          <t>88.35</t>
+        </is>
+      </c>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>0.3695</t>
+        </is>
+      </c>
+      <c r="BE18" t="inlineStr">
+        <is>
+          <t>0.1577</t>
+        </is>
+      </c>
+      <c r="BF18" t="inlineStr">
+        <is>
+          <t>29.92</t>
+        </is>
+      </c>
       <c r="BG18" t="inlineStr"/>
       <c r="BH18" t="inlineStr"/>
       <c r="BI18" t="inlineStr">
@@ -10142,11 +10754,23 @@
           <t>9</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Shawn Armstrong</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>542888</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L19" t="n">
-        <v>29.4</v>
+        <v>27.3</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -10167,7 +10791,7 @@
         <v>5.6</v>
       </c>
       <c r="Q19" t="n">
-        <v>40.2</v>
+        <v>31.5</v>
       </c>
       <c r="R19" t="n">
         <v>27.6</v>
@@ -10218,7 +10842,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr"/>
@@ -10255,7 +10879,7 @@
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
@@ -10328,12 +10952,36 @@
           <t>0.0829</t>
         </is>
       </c>
-      <c r="BA19" t="inlineStr"/>
-      <c r="BB19" t="inlineStr"/>
-      <c r="BC19" t="inlineStr"/>
-      <c r="BD19" t="inlineStr"/>
-      <c r="BE19" t="inlineStr"/>
-      <c r="BF19" t="inlineStr"/>
+      <c r="BA19" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="BB19" t="inlineStr">
+        <is>
+          <t>35.04</t>
+        </is>
+      </c>
+      <c r="BC19" t="inlineStr">
+        <is>
+          <t>88.35</t>
+        </is>
+      </c>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>0.3695</t>
+        </is>
+      </c>
+      <c r="BE19" t="inlineStr">
+        <is>
+          <t>0.1577</t>
+        </is>
+      </c>
+      <c r="BF19" t="inlineStr">
+        <is>
+          <t>29.92</t>
+        </is>
+      </c>
       <c r="BG19" t="inlineStr"/>
       <c r="BH19" t="inlineStr"/>
       <c r="BI19" t="inlineStr">

--- a/outputs/daily/hr_rankings_2026-10-16.xlsx
+++ b/outputs/daily/hr_rankings_2026-10-16.xlsx
@@ -760,12 +760,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -784,7 +784,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>51.5</v>
+        <v>54.3</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -808,10 +808,10 @@
         <v>32</v>
       </c>
       <c r="R2" t="n">
-        <v>27.6</v>
+        <v>43.6</v>
       </c>
       <c r="S2" t="n">
-        <v>92.09999999999999</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T2" t="n">
         <v>50</v>
@@ -821,39 +821,35 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -996,8 +992,16 @@
           <t>29.92</t>
         </is>
       </c>
-      <c r="BG2" t="inlineStr"/>
-      <c r="BH2" t="inlineStr"/>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
       <c r="BI2" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -1036,7 +1040,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1060,7 +1064,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1074,7 +1078,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -1084,10 +1088,10 @@
         <v>32</v>
       </c>
       <c r="R3" t="n">
-        <v>27.6</v>
+        <v>43.6</v>
       </c>
       <c r="S3" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T3" t="n">
         <v>80</v>
@@ -1097,39 +1101,35 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1272,8 +1272,16 @@
           <t>29.92</t>
         </is>
       </c>
-      <c r="BG3" t="inlineStr"/>
-      <c r="BH3" t="inlineStr"/>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
       <c r="BI3" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -1312,7 +1320,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1336,7 +1344,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>48.9</v>
+        <v>51.9</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1350,7 +1358,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -1360,10 +1368,10 @@
         <v>34.3</v>
       </c>
       <c r="R4" t="n">
-        <v>27.6</v>
+        <v>43.6</v>
       </c>
       <c r="S4" t="n">
-        <v>90.40000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T4" t="n">
         <v>50</v>
@@ -1373,39 +1381,35 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1548,8 +1552,16 @@
           <t>28.96</t>
         </is>
       </c>
-      <c r="BG4" t="inlineStr"/>
-      <c r="BH4" t="inlineStr"/>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
       <c r="BI4" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -1588,7 +1600,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1612,7 +1624,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>46.9</v>
+        <v>49.9</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1626,7 +1638,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -1636,10 +1648,10 @@
         <v>34.3</v>
       </c>
       <c r="R5" t="n">
-        <v>27.6</v>
+        <v>43.6</v>
       </c>
       <c r="S5" t="n">
-        <v>92.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T5" t="n">
         <v>80</v>
@@ -1649,39 +1661,35 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -1824,8 +1832,16 @@
           <t>28.96</t>
         </is>
       </c>
-      <c r="BG5" t="inlineStr"/>
-      <c r="BH5" t="inlineStr"/>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
       <c r="BI5" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -1844,7 +1860,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Victor Mesa</t>
+          <t>Victor Mesa Jr.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1864,7 +1880,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1888,7 +1904,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>46.2</v>
+        <v>49.2</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1902,7 +1918,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P6" t="n">
@@ -1912,10 +1928,10 @@
         <v>32</v>
       </c>
       <c r="R6" t="n">
-        <v>27.6</v>
+        <v>43.6</v>
       </c>
       <c r="S6" t="n">
-        <v>71.7</v>
+        <v>76.2</v>
       </c>
       <c r="T6" t="n">
         <v>80</v>
@@ -1925,39 +1941,35 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2100,8 +2112,16 @@
           <t>29.92</t>
         </is>
       </c>
-      <c r="BG6" t="inlineStr"/>
-      <c r="BH6" t="inlineStr"/>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
       <c r="BI6" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -2140,7 +2160,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -2164,7 +2184,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>43.5</v>
+        <v>46.6</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -2178,7 +2198,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P7" t="n">
@@ -2188,10 +2208,10 @@
         <v>34.3</v>
       </c>
       <c r="R7" t="n">
-        <v>27.6</v>
+        <v>43.6</v>
       </c>
       <c r="S7" t="n">
-        <v>81.90000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T7" t="n">
         <v>80</v>
@@ -2201,39 +2221,35 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2376,8 +2392,16 @@
           <t>28.96</t>
         </is>
       </c>
-      <c r="BG7" t="inlineStr"/>
-      <c r="BH7" t="inlineStr"/>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
       <c r="BI7" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -2396,7 +2420,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Yandy Diaz</t>
+          <t>Yandy Díaz</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -2416,7 +2440,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -2440,7 +2464,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>43.3</v>
+        <v>46.3</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2454,7 +2478,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P8" t="n">
@@ -2464,10 +2488,10 @@
         <v>32</v>
       </c>
       <c r="R8" t="n">
-        <v>27.6</v>
+        <v>43.6</v>
       </c>
       <c r="S8" t="n">
-        <v>88.7</v>
+        <v>93.2</v>
       </c>
       <c r="T8" t="n">
         <v>50</v>
@@ -2477,39 +2501,35 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2652,8 +2672,16 @@
           <t>29.92</t>
         </is>
       </c>
-      <c r="BG8" t="inlineStr"/>
-      <c r="BH8" t="inlineStr"/>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
       <c r="BI8" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -2672,7 +2700,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Jose Ramirez</t>
+          <t>José Ramírez</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2692,7 +2720,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -2716,7 +2744,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>41.7</v>
+        <v>44.8</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -2730,7 +2758,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P9" t="n">
@@ -2740,10 +2768,10 @@
         <v>32.5</v>
       </c>
       <c r="R9" t="n">
-        <v>27.6</v>
+        <v>43.6</v>
       </c>
       <c r="S9" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T9" t="n">
         <v>75</v>
@@ -2753,39 +2781,35 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2928,8 +2952,16 @@
           <t>28.96</t>
         </is>
       </c>
-      <c r="BG9" t="inlineStr"/>
-      <c r="BH9" t="inlineStr"/>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
       <c r="BI9" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -2968,12 +3000,12 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -2992,7 +3024,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>38.5</v>
+        <v>43.2</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -3006,7 +3038,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P10" t="n">
@@ -3016,10 +3048,10 @@
         <v>32.5</v>
       </c>
       <c r="R10" t="n">
-        <v>27.6</v>
+        <v>43.6</v>
       </c>
       <c r="S10" t="n">
-        <v>47.9</v>
+        <v>64.3</v>
       </c>
       <c r="T10" t="n">
         <v>75</v>
@@ -3029,39 +3061,35 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3204,8 +3232,16 @@
           <t>28.96</t>
         </is>
       </c>
-      <c r="BG10" t="inlineStr"/>
-      <c r="BH10" t="inlineStr"/>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
       <c r="BI10" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -3219,12 +3255,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>682657</t>
+          <t>683953</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Angel Martinez</t>
+          <t>Travis Bazzana</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -3244,7 +3280,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -3268,7 +3304,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>38.1</v>
+        <v>40.2</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3282,65 +3318,61 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>22.9</v>
+        <v>20.9</v>
       </c>
       <c r="Q11" t="n">
-        <v>32.5</v>
+        <v>34.3</v>
       </c>
       <c r="R11" t="n">
-        <v>27.6</v>
+        <v>43.6</v>
       </c>
       <c r="S11" t="n">
-        <v>71.7</v>
+        <v>76.2</v>
       </c>
       <c r="T11" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U11" t="n">
-        <v>36.3</v>
+        <v>12</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr"/>
@@ -3357,7 +3389,7 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
@@ -3367,17 +3399,17 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/25, 1 HR</t>
+          <t>Last 7 games: 5/25, 0 HR</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
@@ -3387,67 +3419,67 @@
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>6.09</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>33.64</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>87.38</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>98.404</t>
+          <t>98.2866</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.3746</t>
+          <t>0.347</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>0.1347</t>
+          <t>0.123</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>0.2858</t>
+          <t>0.299</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>71.08</t>
+          <t>69.7</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>15.88</t>
+          <t>12.2</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>44.74</t>
+          <t>38.9</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>26.8</t>
+          <t>28.8</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>15.9</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>0.1882</t>
+          <t>0.163</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
@@ -3480,8 +3512,16 @@
           <t>28.96</t>
         </is>
       </c>
-      <c r="BG11" t="inlineStr"/>
-      <c r="BH11" t="inlineStr"/>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
       <c r="BI11" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -3495,12 +3535,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>683953</t>
+          <t>680757</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Travis Bazzana</t>
+          <t>Steven Kwan</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -3520,12 +3560,12 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -3544,7 +3584,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>35.5</v>
+        <v>38.1</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -3558,65 +3598,61 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>20.9</v>
+        <v>2.9</v>
       </c>
       <c r="Q12" t="n">
         <v>34.3</v>
       </c>
       <c r="R12" t="n">
-        <v>27.6</v>
+        <v>43.6</v>
       </c>
       <c r="S12" t="n">
-        <v>59.8</v>
+        <v>93.2</v>
       </c>
       <c r="T12" t="n">
         <v>80</v>
       </c>
       <c r="U12" t="n">
-        <v>12</v>
+        <v>43.1</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr"/>
@@ -3633,12 +3669,12 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -3648,7 +3684,7 @@
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/25, 0 HR</t>
+          <t>Contact streak: 11/27 over last 7 games</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
@@ -3663,67 +3699,67 @@
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>36.2</t>
+          <t>13.14</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>84.59</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>98.2866</t>
+          <t>92.8324</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.347</t>
+          <t>0.3499</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>0.0741</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.299</t>
+          <t>0.3226</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>62.73</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>27.81</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>28.8</t>
+          <t>23.44</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>0.163</t>
+          <t>0.0775</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
@@ -3756,8 +3792,16 @@
           <t>28.96</t>
         </is>
       </c>
-      <c r="BG12" t="inlineStr"/>
-      <c r="BH12" t="inlineStr"/>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
       <c r="BI12" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -3796,12 +3840,12 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -3820,7 +3864,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>35.2</v>
+        <v>37.1</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -3834,7 +3878,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P13" t="n">
@@ -3844,10 +3888,10 @@
         <v>32</v>
       </c>
       <c r="R13" t="n">
-        <v>27.6</v>
+        <v>43.6</v>
       </c>
       <c r="S13" t="n">
-        <v>90.40000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T13" t="n">
         <v>80</v>
@@ -3857,39 +3901,35 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4032,8 +4072,16 @@
           <t>29.92</t>
         </is>
       </c>
-      <c r="BG13" t="inlineStr"/>
-      <c r="BH13" t="inlineStr"/>
+      <c r="BG13" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
       <c r="BI13" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -4047,24 +4095,24 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>680757</t>
+          <t>802415</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Steven Kwan</t>
+          <t>Chandler Simpson</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>2026-10-17T00:00:00Z</t>
@@ -4072,22 +4120,22 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Nick Martinez</t>
+          <t>Shawn Armstrong</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>607259</t>
+          <t>542888</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -4096,7 +4144,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>35.1</v>
+        <v>35.8</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -4110,62 +4158,58 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>2.9</v>
+        <v>0.2</v>
       </c>
       <c r="Q14" t="n">
-        <v>34.3</v>
+        <v>32</v>
       </c>
       <c r="R14" t="n">
-        <v>27.6</v>
+        <v>43.6</v>
       </c>
       <c r="S14" t="n">
-        <v>88.7</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T14" t="n">
         <v>80</v>
       </c>
       <c r="U14" t="n">
-        <v>43.1</v>
+        <v>15.3</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4185,7 +4229,7 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
@@ -4200,12 +4244,12 @@
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Contact streak: 11/27 over last 7 games</t>
+          <t>Last 7 games: 6/27, 0 HR</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
@@ -4215,101 +4259,109 @@
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>13.14</t>
+          <t>14.71</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>84.59</t>
+          <t>83.88</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>92.8324</t>
+          <t>92.929</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>0.3499</t>
+          <t>0.3087</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>0.0741</t>
+          <t>0.0382</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.3226</t>
+          <t>0.2732</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>62.73</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>27.81</t>
+          <t>28.27</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>23.44</t>
+          <t>12.51</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>0.0775</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>6.86</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>33.38</t>
+          <t>35.04</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>87.39</t>
+          <t>88.35</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>0.4114</t>
+          <t>0.3695</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
-          <t>0.1502</t>
+          <t>0.1577</t>
         </is>
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>28.96</t>
-        </is>
-      </c>
-      <c r="BG14" t="inlineStr"/>
-      <c r="BH14" t="inlineStr"/>
+          <t>29.92</t>
+        </is>
+      </c>
+      <c r="BG14" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
       <c r="BI14" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -4348,7 +4400,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -4372,7 +4424,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>32.5</v>
+        <v>35.5</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -4386,7 +4438,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P15" t="n">
@@ -4396,10 +4448,10 @@
         <v>32.5</v>
       </c>
       <c r="R15" t="n">
-        <v>27.6</v>
+        <v>43.6</v>
       </c>
       <c r="S15" t="n">
-        <v>40.2</v>
+        <v>44.8</v>
       </c>
       <c r="T15" t="n">
         <v>75</v>
@@ -4409,39 +4461,35 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4584,8 +4632,16 @@
           <t>28.96</t>
         </is>
       </c>
-      <c r="BG15" t="inlineStr"/>
-      <c r="BH15" t="inlineStr"/>
+      <c r="BG15" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
       <c r="BI15" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -4599,12 +4655,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>680700</t>
+          <t>676356</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Richie Palacios</t>
+          <t>Jonny DeLuca</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -4624,12 +4680,12 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -4648,7 +4704,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>31.8</v>
+        <v>34.8</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -4662,62 +4718,58 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>15.4</v>
+        <v>10.6</v>
       </c>
       <c r="Q16" t="n">
         <v>32</v>
       </c>
       <c r="R16" t="n">
-        <v>27.6</v>
+        <v>43.6</v>
       </c>
       <c r="S16" t="n">
-        <v>47.9</v>
+        <v>64.3</v>
       </c>
       <c r="T16" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U16" t="n">
-        <v>19.5</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4737,27 +4789,27 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/20, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
@@ -4767,67 +4819,67 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>4.57</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>33.39</t>
+          <t>30.68</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>87.31</t>
+          <t>85.74</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>97.1084</t>
+          <t>97.7063</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.3655</t>
+          <t>0.3262</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>0.1018</t>
+          <t>0.0879</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.3213</t>
+          <t>0.2628</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>68.91</t>
+          <t>72.75</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>28.03</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>37.09</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>20.98</t>
+          <t>22.55</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>0.133</t>
+          <t>0.151</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
@@ -4860,8 +4912,16 @@
           <t>29.92</t>
         </is>
       </c>
-      <c r="BG16" t="inlineStr"/>
-      <c r="BH16" t="inlineStr"/>
+      <c r="BG16" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH16" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
       <c r="BI16" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -4875,12 +4935,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>676356</t>
+          <t>680700</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Jonny DeLuca</t>
+          <t>Richie Palacios</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -4900,12 +4960,12 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -4924,7 +4984,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>31.7</v>
+        <v>34.8</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -4938,62 +4998,58 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup, Hot Hitter/Streak</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>10.6</v>
+        <v>15.4</v>
       </c>
       <c r="Q17" t="n">
         <v>32</v>
       </c>
       <c r="R17" t="n">
-        <v>27.6</v>
+        <v>43.6</v>
       </c>
       <c r="S17" t="n">
-        <v>59.8</v>
+        <v>52.4</v>
       </c>
       <c r="T17" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U17" t="n">
-        <v>70.59999999999999</v>
+        <v>19.5</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -5013,27 +5069,27 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 5/20, 0 HR</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
@@ -5043,67 +5099,67 @@
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>30.68</t>
+          <t>33.39</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>85.74</t>
+          <t>87.31</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>97.7063</t>
+          <t>97.1084</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.3262</t>
+          <t>0.3655</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>0.0879</t>
+          <t>0.1018</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.2628</t>
+          <t>0.3213</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>72.75</t>
+          <t>68.91</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>28.03</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>37.09</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>22.55</t>
+          <t>20.98</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>0.133</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
@@ -5136,8 +5192,16 @@
           <t>29.92</t>
         </is>
       </c>
-      <c r="BG17" t="inlineStr"/>
-      <c r="BH17" t="inlineStr"/>
+      <c r="BG17" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH17" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
       <c r="BI17" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -5151,24 +5215,24 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>802415</t>
+          <t>690984</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Chandler Simpson</t>
+          <t>Petey Halpin</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F18" t="inlineStr">
         <is>
           <t>2026-10-17T00:00:00Z</t>
@@ -5176,22 +5240,22 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Shawn Armstrong</t>
+          <t>Nick Martinez</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>542888</t>
+          <t>607259</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -5200,7 +5264,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>31.3</v>
+        <v>33.6</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -5214,62 +5278,58 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0.2</v>
+        <v>7.1</v>
       </c>
       <c r="Q18" t="n">
-        <v>32</v>
+        <v>34.3</v>
       </c>
       <c r="R18" t="n">
-        <v>27.6</v>
+        <v>43.6</v>
       </c>
       <c r="S18" t="n">
-        <v>81.90000000000001</v>
+        <v>52.4</v>
       </c>
       <c r="T18" t="n">
         <v>80</v>
       </c>
       <c r="U18" t="n">
-        <v>15.3</v>
+        <v>38.3</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -5289,12 +5349,12 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
@@ -5304,12 +5364,12 @@
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/27, 0 HR</t>
+          <t>Contact streak: 3/8 over last 7 games</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
@@ -5319,101 +5379,109 @@
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>14.71</t>
+          <t>17.85</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>83.88</t>
+          <t>81.45</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>92.929</t>
+          <t>93.4449</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.3087</t>
+          <t>0.3143</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>0.0382</t>
+          <t>0.0924</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.2732</t>
+          <t>0.2902</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>64.8</t>
+          <t>70.22</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>5.46</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>40.34</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>12.51</t>
+          <t>31.02</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.0707</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>6.86</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>35.04</t>
+          <t>33.38</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>88.35</t>
+          <t>87.39</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>0.3695</t>
+          <t>0.4114</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
-          <t>0.1577</t>
+          <t>0.1502</t>
         </is>
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>29.92</t>
-        </is>
-      </c>
-      <c r="BG18" t="inlineStr"/>
-      <c r="BH18" t="inlineStr"/>
+          <t>28.96</t>
+        </is>
+      </c>
+      <c r="BG18" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH18" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
       <c r="BI18" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -5452,7 +5520,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -5476,7 +5544,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>27.3</v>
+        <v>30.3</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -5490,7 +5558,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P19" t="n">
@@ -5500,10 +5568,10 @@
         <v>31.5</v>
       </c>
       <c r="R19" t="n">
-        <v>27.6</v>
+        <v>43.6</v>
       </c>
       <c r="S19" t="n">
-        <v>40.2</v>
+        <v>44.8</v>
       </c>
       <c r="T19" t="n">
         <v>75</v>
@@ -5513,39 +5581,35 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -5688,8 +5752,16 @@
           <t>29.92</t>
         </is>
       </c>
-      <c r="BG19" t="inlineStr"/>
-      <c r="BH19" t="inlineStr"/>
+      <c r="BG19" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
       <c r="BI19" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -6054,12 +6126,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -6078,7 +6150,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>51.5</v>
+        <v>54.3</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -6092,7 +6164,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -6102,10 +6174,10 @@
         <v>32</v>
       </c>
       <c r="R2" t="n">
-        <v>27.6</v>
+        <v>43.6</v>
       </c>
       <c r="S2" t="n">
-        <v>92.09999999999999</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T2" t="n">
         <v>50</v>
@@ -6115,39 +6187,35 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6290,8 +6358,16 @@
           <t>29.92</t>
         </is>
       </c>
-      <c r="BG2" t="inlineStr"/>
-      <c r="BH2" t="inlineStr"/>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
       <c r="BI2" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -6330,7 +6406,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -6354,7 +6430,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -6368,7 +6444,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -6378,10 +6454,10 @@
         <v>32</v>
       </c>
       <c r="R3" t="n">
-        <v>27.6</v>
+        <v>43.6</v>
       </c>
       <c r="S3" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T3" t="n">
         <v>80</v>
@@ -6391,39 +6467,35 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6566,8 +6638,16 @@
           <t>29.92</t>
         </is>
       </c>
-      <c r="BG3" t="inlineStr"/>
-      <c r="BH3" t="inlineStr"/>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
       <c r="BI3" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -6606,7 +6686,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -6630,7 +6710,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>48.9</v>
+        <v>51.9</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -6644,7 +6724,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -6654,10 +6734,10 @@
         <v>34.3</v>
       </c>
       <c r="R4" t="n">
-        <v>27.6</v>
+        <v>43.6</v>
       </c>
       <c r="S4" t="n">
-        <v>90.40000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T4" t="n">
         <v>50</v>
@@ -6667,39 +6747,35 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6842,8 +6918,16 @@
           <t>28.96</t>
         </is>
       </c>
-      <c r="BG4" t="inlineStr"/>
-      <c r="BH4" t="inlineStr"/>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
       <c r="BI4" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -6882,7 +6966,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -6906,7 +6990,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>46.9</v>
+        <v>49.9</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -6920,7 +7004,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -6930,10 +7014,10 @@
         <v>34.3</v>
       </c>
       <c r="R5" t="n">
-        <v>27.6</v>
+        <v>43.6</v>
       </c>
       <c r="S5" t="n">
-        <v>92.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T5" t="n">
         <v>80</v>
@@ -6943,39 +7027,35 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -7118,8 +7198,16 @@
           <t>28.96</t>
         </is>
       </c>
-      <c r="BG5" t="inlineStr"/>
-      <c r="BH5" t="inlineStr"/>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
       <c r="BI5" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -7138,7 +7226,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Victor Mesa</t>
+          <t>Victor Mesa Jr.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -7158,7 +7246,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -7182,7 +7270,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>46.2</v>
+        <v>49.2</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -7196,7 +7284,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P6" t="n">
@@ -7206,10 +7294,10 @@
         <v>32</v>
       </c>
       <c r="R6" t="n">
-        <v>27.6</v>
+        <v>43.6</v>
       </c>
       <c r="S6" t="n">
-        <v>71.7</v>
+        <v>76.2</v>
       </c>
       <c r="T6" t="n">
         <v>80</v>
@@ -7219,39 +7307,35 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7394,8 +7478,16 @@
           <t>29.92</t>
         </is>
       </c>
-      <c r="BG6" t="inlineStr"/>
-      <c r="BH6" t="inlineStr"/>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
       <c r="BI6" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -7434,7 +7526,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -7458,7 +7550,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>43.5</v>
+        <v>46.6</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -7472,7 +7564,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P7" t="n">
@@ -7482,10 +7574,10 @@
         <v>34.3</v>
       </c>
       <c r="R7" t="n">
-        <v>27.6</v>
+        <v>43.6</v>
       </c>
       <c r="S7" t="n">
-        <v>81.90000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T7" t="n">
         <v>80</v>
@@ -7495,39 +7587,35 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7670,8 +7758,16 @@
           <t>28.96</t>
         </is>
       </c>
-      <c r="BG7" t="inlineStr"/>
-      <c r="BH7" t="inlineStr"/>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
       <c r="BI7" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -7690,7 +7786,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Yandy Diaz</t>
+          <t>Yandy Díaz</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -7710,7 +7806,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -7734,7 +7830,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>43.3</v>
+        <v>46.3</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -7748,7 +7844,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P8" t="n">
@@ -7758,10 +7854,10 @@
         <v>32</v>
       </c>
       <c r="R8" t="n">
-        <v>27.6</v>
+        <v>43.6</v>
       </c>
       <c r="S8" t="n">
-        <v>88.7</v>
+        <v>93.2</v>
       </c>
       <c r="T8" t="n">
         <v>50</v>
@@ -7771,39 +7867,35 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7946,8 +8038,16 @@
           <t>29.92</t>
         </is>
       </c>
-      <c r="BG8" t="inlineStr"/>
-      <c r="BH8" t="inlineStr"/>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
       <c r="BI8" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -7966,7 +8066,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Jose Ramirez</t>
+          <t>José Ramírez</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -7986,7 +8086,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -8010,7 +8110,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>41.7</v>
+        <v>44.8</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -8024,7 +8124,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P9" t="n">
@@ -8034,10 +8134,10 @@
         <v>32.5</v>
       </c>
       <c r="R9" t="n">
-        <v>27.6</v>
+        <v>43.6</v>
       </c>
       <c r="S9" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T9" t="n">
         <v>75</v>
@@ -8047,39 +8147,35 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8222,8 +8318,16 @@
           <t>28.96</t>
         </is>
       </c>
-      <c r="BG9" t="inlineStr"/>
-      <c r="BH9" t="inlineStr"/>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
       <c r="BI9" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -8262,12 +8366,12 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -8286,7 +8390,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>38.5</v>
+        <v>43.2</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -8300,7 +8404,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P10" t="n">
@@ -8310,10 +8414,10 @@
         <v>32.5</v>
       </c>
       <c r="R10" t="n">
-        <v>27.6</v>
+        <v>43.6</v>
       </c>
       <c r="S10" t="n">
-        <v>47.9</v>
+        <v>64.3</v>
       </c>
       <c r="T10" t="n">
         <v>75</v>
@@ -8323,39 +8427,35 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8498,8 +8598,16 @@
           <t>28.96</t>
         </is>
       </c>
-      <c r="BG10" t="inlineStr"/>
-      <c r="BH10" t="inlineStr"/>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
       <c r="BI10" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -8513,12 +8621,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>682657</t>
+          <t>683953</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Angel Martinez</t>
+          <t>Travis Bazzana</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -8538,7 +8646,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -8562,7 +8670,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>38.1</v>
+        <v>40.2</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -8576,65 +8684,61 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>22.9</v>
+        <v>20.9</v>
       </c>
       <c r="Q11" t="n">
-        <v>32.5</v>
+        <v>34.3</v>
       </c>
       <c r="R11" t="n">
-        <v>27.6</v>
+        <v>43.6</v>
       </c>
       <c r="S11" t="n">
-        <v>71.7</v>
+        <v>76.2</v>
       </c>
       <c r="T11" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U11" t="n">
-        <v>36.3</v>
+        <v>12</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr"/>
@@ -8651,7 +8755,7 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
@@ -8661,17 +8765,17 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/25, 1 HR</t>
+          <t>Last 7 games: 5/25, 0 HR</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
@@ -8681,67 +8785,67 @@
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>6.09</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>33.64</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>87.38</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>98.404</t>
+          <t>98.2866</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.3746</t>
+          <t>0.347</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>0.1347</t>
+          <t>0.123</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>0.2858</t>
+          <t>0.299</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>71.08</t>
+          <t>69.7</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>15.88</t>
+          <t>12.2</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>44.74</t>
+          <t>38.9</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>26.8</t>
+          <t>28.8</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>15.9</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>0.1882</t>
+          <t>0.163</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
@@ -8774,8 +8878,16 @@
           <t>28.96</t>
         </is>
       </c>
-      <c r="BG11" t="inlineStr"/>
-      <c r="BH11" t="inlineStr"/>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
       <c r="BI11" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -8789,12 +8901,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>683953</t>
+          <t>680757</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Travis Bazzana</t>
+          <t>Steven Kwan</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -8814,12 +8926,12 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -8838,7 +8950,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>35.5</v>
+        <v>38.1</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -8852,65 +8964,61 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>20.9</v>
+        <v>2.9</v>
       </c>
       <c r="Q12" t="n">
         <v>34.3</v>
       </c>
       <c r="R12" t="n">
-        <v>27.6</v>
+        <v>43.6</v>
       </c>
       <c r="S12" t="n">
-        <v>59.8</v>
+        <v>93.2</v>
       </c>
       <c r="T12" t="n">
         <v>80</v>
       </c>
       <c r="U12" t="n">
-        <v>12</v>
+        <v>43.1</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr"/>
@@ -8927,12 +9035,12 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -8942,7 +9050,7 @@
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/25, 0 HR</t>
+          <t>Contact streak: 11/27 over last 7 games</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
@@ -8957,67 +9065,67 @@
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>36.2</t>
+          <t>13.14</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>84.59</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>98.2866</t>
+          <t>92.8324</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.347</t>
+          <t>0.3499</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>0.0741</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.299</t>
+          <t>0.3226</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>62.73</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>27.81</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>28.8</t>
+          <t>23.44</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>0.163</t>
+          <t>0.0775</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
@@ -9050,8 +9158,16 @@
           <t>28.96</t>
         </is>
       </c>
-      <c r="BG12" t="inlineStr"/>
-      <c r="BH12" t="inlineStr"/>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
       <c r="BI12" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -9090,12 +9206,12 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -9114,7 +9230,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>35.2</v>
+        <v>37.1</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -9128,7 +9244,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P13" t="n">
@@ -9138,10 +9254,10 @@
         <v>32</v>
       </c>
       <c r="R13" t="n">
-        <v>27.6</v>
+        <v>43.6</v>
       </c>
       <c r="S13" t="n">
-        <v>90.40000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T13" t="n">
         <v>80</v>
@@ -9151,39 +9267,35 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9326,8 +9438,16 @@
           <t>29.92</t>
         </is>
       </c>
-      <c r="BG13" t="inlineStr"/>
-      <c r="BH13" t="inlineStr"/>
+      <c r="BG13" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
       <c r="BI13" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -9341,24 +9461,24 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>680757</t>
+          <t>802415</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Steven Kwan</t>
+          <t>Chandler Simpson</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>2026-10-17T00:00:00Z</t>
@@ -9366,22 +9486,22 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Nick Martinez</t>
+          <t>Shawn Armstrong</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>607259</t>
+          <t>542888</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -9390,7 +9510,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>35.1</v>
+        <v>35.8</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -9404,62 +9524,58 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>2.9</v>
+        <v>0.2</v>
       </c>
       <c r="Q14" t="n">
-        <v>34.3</v>
+        <v>32</v>
       </c>
       <c r="R14" t="n">
-        <v>27.6</v>
+        <v>43.6</v>
       </c>
       <c r="S14" t="n">
-        <v>88.7</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T14" t="n">
         <v>80</v>
       </c>
       <c r="U14" t="n">
-        <v>43.1</v>
+        <v>15.3</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9479,7 +9595,7 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
@@ -9494,12 +9610,12 @@
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Contact streak: 11/27 over last 7 games</t>
+          <t>Last 7 games: 6/27, 0 HR</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
@@ -9509,101 +9625,109 @@
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>13.14</t>
+          <t>14.71</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>84.59</t>
+          <t>83.88</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>92.8324</t>
+          <t>92.929</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>0.3499</t>
+          <t>0.3087</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>0.0741</t>
+          <t>0.0382</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.3226</t>
+          <t>0.2732</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>62.73</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>27.81</t>
+          <t>28.27</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>23.44</t>
+          <t>12.51</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>0.0775</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>6.86</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>33.38</t>
+          <t>35.04</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>87.39</t>
+          <t>88.35</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>0.4114</t>
+          <t>0.3695</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
-          <t>0.1502</t>
+          <t>0.1577</t>
         </is>
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>28.96</t>
-        </is>
-      </c>
-      <c r="BG14" t="inlineStr"/>
-      <c r="BH14" t="inlineStr"/>
+          <t>29.92</t>
+        </is>
+      </c>
+      <c r="BG14" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
       <c r="BI14" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -9642,7 +9766,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -9666,7 +9790,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>32.5</v>
+        <v>35.5</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -9680,7 +9804,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P15" t="n">
@@ -9690,10 +9814,10 @@
         <v>32.5</v>
       </c>
       <c r="R15" t="n">
-        <v>27.6</v>
+        <v>43.6</v>
       </c>
       <c r="S15" t="n">
-        <v>40.2</v>
+        <v>44.8</v>
       </c>
       <c r="T15" t="n">
         <v>75</v>
@@ -9703,39 +9827,35 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9878,8 +9998,16 @@
           <t>28.96</t>
         </is>
       </c>
-      <c r="BG15" t="inlineStr"/>
-      <c r="BH15" t="inlineStr"/>
+      <c r="BG15" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
       <c r="BI15" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -9893,12 +10021,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>680700</t>
+          <t>676356</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Richie Palacios</t>
+          <t>Jonny DeLuca</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -9918,12 +10046,12 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -9942,7 +10070,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>31.8</v>
+        <v>34.8</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -9956,62 +10084,58 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>15.4</v>
+        <v>10.6</v>
       </c>
       <c r="Q16" t="n">
         <v>32</v>
       </c>
       <c r="R16" t="n">
-        <v>27.6</v>
+        <v>43.6</v>
       </c>
       <c r="S16" t="n">
-        <v>47.9</v>
+        <v>64.3</v>
       </c>
       <c r="T16" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U16" t="n">
-        <v>19.5</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10031,27 +10155,27 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/20, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
@@ -10061,67 +10185,67 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>4.57</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>33.39</t>
+          <t>30.68</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>87.31</t>
+          <t>85.74</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>97.1084</t>
+          <t>97.7063</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.3655</t>
+          <t>0.3262</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>0.1018</t>
+          <t>0.0879</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.3213</t>
+          <t>0.2628</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>68.91</t>
+          <t>72.75</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>28.03</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>37.09</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>20.98</t>
+          <t>22.55</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>0.133</t>
+          <t>0.151</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
@@ -10154,8 +10278,16 @@
           <t>29.92</t>
         </is>
       </c>
-      <c r="BG16" t="inlineStr"/>
-      <c r="BH16" t="inlineStr"/>
+      <c r="BG16" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH16" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
       <c r="BI16" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -10169,12 +10301,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>676356</t>
+          <t>680700</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Jonny DeLuca</t>
+          <t>Richie Palacios</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -10194,12 +10326,12 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -10218,7 +10350,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>31.7</v>
+        <v>34.8</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -10232,62 +10364,58 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup, Hot Hitter/Streak</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>10.6</v>
+        <v>15.4</v>
       </c>
       <c r="Q17" t="n">
         <v>32</v>
       </c>
       <c r="R17" t="n">
-        <v>27.6</v>
+        <v>43.6</v>
       </c>
       <c r="S17" t="n">
-        <v>59.8</v>
+        <v>52.4</v>
       </c>
       <c r="T17" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U17" t="n">
-        <v>70.59999999999999</v>
+        <v>19.5</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10307,27 +10435,27 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 5/20, 0 HR</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
@@ -10337,67 +10465,67 @@
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>30.68</t>
+          <t>33.39</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>85.74</t>
+          <t>87.31</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>97.7063</t>
+          <t>97.1084</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.3262</t>
+          <t>0.3655</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>0.0879</t>
+          <t>0.1018</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.2628</t>
+          <t>0.3213</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>72.75</t>
+          <t>68.91</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>28.03</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>37.09</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>22.55</t>
+          <t>20.98</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>0.133</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
@@ -10430,8 +10558,16 @@
           <t>29.92</t>
         </is>
       </c>
-      <c r="BG17" t="inlineStr"/>
-      <c r="BH17" t="inlineStr"/>
+      <c r="BG17" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH17" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
       <c r="BI17" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -10445,24 +10581,24 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>802415</t>
+          <t>690984</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Chandler Simpson</t>
+          <t>Petey Halpin</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F18" t="inlineStr">
         <is>
           <t>2026-10-17T00:00:00Z</t>
@@ -10470,22 +10606,22 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Shawn Armstrong</t>
+          <t>Nick Martinez</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>542888</t>
+          <t>607259</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -10494,7 +10630,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>31.3</v>
+        <v>33.6</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -10508,62 +10644,58 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0.2</v>
+        <v>7.1</v>
       </c>
       <c r="Q18" t="n">
-        <v>32</v>
+        <v>34.3</v>
       </c>
       <c r="R18" t="n">
-        <v>27.6</v>
+        <v>43.6</v>
       </c>
       <c r="S18" t="n">
-        <v>81.90000000000001</v>
+        <v>52.4</v>
       </c>
       <c r="T18" t="n">
         <v>80</v>
       </c>
       <c r="U18" t="n">
-        <v>15.3</v>
+        <v>38.3</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10583,12 +10715,12 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
@@ -10598,12 +10730,12 @@
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/27, 0 HR</t>
+          <t>Contact streak: 3/8 over last 7 games</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
@@ -10613,101 +10745,109 @@
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>14.71</t>
+          <t>17.85</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>83.88</t>
+          <t>81.45</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>92.929</t>
+          <t>93.4449</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.3087</t>
+          <t>0.3143</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>0.0382</t>
+          <t>0.0924</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.2732</t>
+          <t>0.2902</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>64.8</t>
+          <t>70.22</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>5.46</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>40.34</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>12.51</t>
+          <t>31.02</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.0707</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>6.86</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>35.04</t>
+          <t>33.38</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>88.35</t>
+          <t>87.39</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>0.3695</t>
+          <t>0.4114</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
-          <t>0.1577</t>
+          <t>0.1502</t>
         </is>
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>29.92</t>
-        </is>
-      </c>
-      <c r="BG18" t="inlineStr"/>
-      <c r="BH18" t="inlineStr"/>
+          <t>28.96</t>
+        </is>
+      </c>
+      <c r="BG18" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH18" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
       <c r="BI18" t="inlineStr">
         <is>
           <t>Progressive Field</t>
@@ -10746,7 +10886,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -10770,7 +10910,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>27.3</v>
+        <v>30.3</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -10784,7 +10924,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P19" t="n">
@@ -10794,10 +10934,10 @@
         <v>31.5</v>
       </c>
       <c r="R19" t="n">
-        <v>27.6</v>
+        <v>43.6</v>
       </c>
       <c r="S19" t="n">
-        <v>40.2</v>
+        <v>44.8</v>
       </c>
       <c r="T19" t="n">
         <v>75</v>
@@ -10807,39 +10947,35 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10982,8 +11118,16 @@
           <t>29.92</t>
         </is>
       </c>
-      <c r="BG19" t="inlineStr"/>
-      <c r="BH19" t="inlineStr"/>
+      <c r="BG19" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
       <c r="BI19" t="inlineStr">
         <is>
           <t>Progressive Field</t>
